--- a/naver-place-crawler/results_nail/대덕구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/대덕구_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>채우다 네일</t>
+          <t>네일하이</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nail_by_chaeuda@naver.com</t>
+          <t>dojulie@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1322-8628</t>
+          <t>0507-1424-7228</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 비래서로10번길 76 1층.채우다네일</t>
+          <t>대전광역시 대덕구 송촌북로4번길 7-6 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sO65IRDd</t>
+          <t>https://www.instagram.com/nailhi_art</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>38427932</t>
+          <t>2065215101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38427932</t>
+          <t>https://m.place.naver.com/place/2065215101</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>푸스케어 대전신탄진점</t>
+          <t>INDEEDMOOI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fusscaer_sintanjin@naver.com</t>
+          <t>indeedmooi@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1440-9218</t>
+          <t>0507-1346-6424</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전 대덕구 석봉로37번길 30 2층</t>
+          <t>대전광역시 대덕구 한밭대로1117번길 40 힙티크 1층 인디드무이</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fusscaer_sintanjin</t>
+          <t>https://www.instagram.com/indeed_mooi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wbpka4d</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>68</v>
+        <v>198</v>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1217159353</t>
+          <t>1114773269</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1217159353</t>
+          <t>https://m.place.naver.com/place/1114773269</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -756,24 +752,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일루아</t>
+          <t>뷰티사이언스네일몰</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wldud0735@naver.com</t>
+          <t>bcsacademy@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1368-0289</t>
+          <t>0507-1309-3380</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리북로 53 1층</t>
+          <t>대전광역시 대덕구 한남로 65 나동 3층 1호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1798664755</t>
+          <t>1509821692</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798664755</t>
+          <t>https://m.place.naver.com/place/1509821692</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -850,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>루비에뷰티</t>
+          <t>디앤네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eunhee_nail@naver.com</t>
+          <t>leo-tiger@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1359-5249</t>
+          <t>0507-1336-7196</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전 대덕구 신탄진북로32번길 14 1층</t>
+          <t>대전광역시 대덕구 석봉로37번길 50 1층 건물</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eunhee_nail/224177918242</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -882,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2028310053</t>
+          <t>1079560024</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028310053</t>
+          <t>https://m.place.naver.com/place/1079560024</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -944,39 +940,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일 쁘 셀</t>
+          <t>마벨네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sulimday@naver.com</t>
+          <t>yelee6080@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1382-2219</t>
+          <t>0507-1338-1863</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 한남로17번길 38</t>
+          <t>대전광역시 대덕구 중리남로8번길 7 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xowGLxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -992,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1598792967</t>
+          <t>1471715037</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598792967</t>
+          <t>https://m.place.naver.com/place/1471715037</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1038,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>끌밋네일</t>
+          <t>미야,네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pmh2317@naver.com</t>
+          <t>asahan214@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1310-0340</t>
+          <t>0507-1373-4162</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전 대덕구 신탄진북로 41 1층</t>
+          <t>대전광역시 대덕구 대덕대로 1555 상가동 1층 102호 미야네일</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sjlRfxXg</t>
+          <t>https://www.instagram.com/miya_nail4162?igsh=MXgzaGhjbmNkOHVvNQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1086,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2007045292</t>
+          <t>1892298393</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007045292</t>
+          <t>https://m.place.naver.com/place/1892298393</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1132,30 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일뮤트</t>
+          <t>엉아네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>seoyoniee22@naver.com</t>
+          <t>c_younga@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0507-1360-5069</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전광역시 동구 백룡로5번길 9 1층 103호</t>
+          <t>대전광역시 대덕구 동춘당로 178 보람코아상가 141호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xeTAyn</t>
+          <t>https://www.instagram.com/eongahnail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,22 +1176,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2093153296</t>
+          <t>1946869133</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2093153296</t>
+          <t>https://m.place.naver.com/place/1946869133</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1222,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>히즈네일</t>
+          <t>빵실네일 &amp; 오로지푸스송촌점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jennyrubyjane_@naver.com</t>
+          <t>nailardi@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1303-8261</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전광역시 서구 도산로403번길 45 1층 히즈네일</t>
+          <t>대전광역시 대덕구 동춘당로48번길 25 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyeez_nail/</t>
+          <t>https://www.instagram.com/nail.0__0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1270,7 +1266,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="R9" t="n">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2033243510</t>
+          <t>177863865</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033243510</t>
+          <t>https://m.place.naver.com/place/177863865</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유안테라피</t>
+          <t>지유네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>oironail@naver.com</t>
+          <t>jiyunail@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1464-1737</t>
+          <t>0507-1431-2433</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전 서구 도솔로335번길 4 101호</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9 1층 151호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uan_trp_?igsh=MWRtcDU5YTh6MGV2bQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,7 +1344,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1369,17 +1365,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2008076870</t>
+          <t>2007138642</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2008076870</t>
+          <t>https://m.place.naver.com/place/2007138642</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1406,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>이프네일</t>
+          <t>네일유엘</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sms5169@naver.com</t>
+          <t>uldesign17@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1312-8951</t>
+          <t>0507-1395-9046</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전 서구 둔산로74번길 27 3층</t>
+          <t>대전광역시 대덕구 석봉로37번길 12 1층 네일유엘</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yKvZX/chat</t>
+          <t>https://www.instagram.com/nail_yu.l</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1452,17 +1448,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wt9sj90</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1471,32 +1463,6090 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>22</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1390260311</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1390260311</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>린네일</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sini_97@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 대청로 61 1층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2002116511</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002116511</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>네일해랑</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ayus_n@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로114번길 9</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1199858879</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1199858879</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>엔에이뷰티</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dang2709@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 석봉로3번길 38 1층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beauty.nail_na</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>393</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>400</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1313449424</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1313449424</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>연네일</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>wlsl9169@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1385-7670</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로114번길 9 111호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_JxbxmAn/chat</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R15" t="n">
+        <v>58</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1111773654</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111773654</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>채우다 네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>nail_by_chaeuda@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1322-8628</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 비래서로10번길 76 1층.채우다네일</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sO65IRDd</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>221</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>38427932</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38427932</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>피카루네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ssisru7@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1356-1782</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 비래동로16번길 27 1층 피카루네일</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://instagram.com/pikaru_nail</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>118</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1453791959</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1453791959</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>끌밋네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>pmh2317@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1310-0340</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진북로 41 1층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sjlRfxXg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R18" t="n">
+        <v>3</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2007045292</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2007045292</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>손톱깎이</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nagi96@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>042-633-6619</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌북로19번길 8-21</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>http://0426336619.tshome.co.kr/menu.php</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>30</v>
+      </c>
+      <c r="R19" t="n">
+        <v>150</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1439652285</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1439652285</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>네일리온드</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mum9177@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1464-1483</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 대청로 43 상가 B동 211호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_PUazG</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2054827797</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2054827797</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="R20" t="n">
+        <v>62</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1568879186</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1568879186</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>네일쿱스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>zmzpop@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진로218번길 25</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1101217149</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1101217149</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>유니즈네일</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gksmfz7@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1328-9654</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 한밭대로1130번길 10 1층 유니즈 네일</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/u_needs_nail</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>35</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1542052913</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1542052913</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>네일뭐해</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mementomori-24@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1362-8739</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로114번길 9 1층 125호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2047980305</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2047980305</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>네일&amp;패디쿱스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>som_a621@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1474-2311</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진로218번길 25 1층 102호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>23</v>
+      </c>
+      <c r="R24" t="n">
+        <v>23</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1009458693</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1009458693</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>러브희</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lbang9@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1449-1391</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 비래동로39번길 9 1층 LUVHEE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/luvhee.nails</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>471</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>472</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1191517495</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1191517495</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>푸스케어 대전신탄진점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fusscaer_sintanjin@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1440-9218</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 석봉로37번길 30 2층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fusscaer_sintanjin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>77</v>
+      </c>
+      <c r="R26" t="n">
+        <v>145</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1217159353</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1217159353</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>리미네일</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>isky6407@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로48번길 22 1층 리미네일</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_yvVCxj</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>130</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1524115972</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1524115972</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>아이러브네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>saddysad@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>042-286-8006</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진로 839</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>12</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1545070428</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1545070428</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>더예쁜네일</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sjynobby@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌북로 6 1층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1236643304</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236643304</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>뷰티쑤</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>eternal_beauty_@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1412-1152</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 비래동로32번길 12 뷰티쑤</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sfumCePe</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>167</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1837401843</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1837401843</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>차밍네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>hyunah0701@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1346-0584</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 한남로 33 1층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/charmingnail__</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2030664237</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2030664237</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>쮸샵</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>herrimi@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>042-345-8384</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 석봉로38번길 13 하늘빛교회</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1125107179</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1125107179</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>네일 쁘 셀</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>orr0427@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1382-2219</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 한남로17번길 38</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xowGLxj</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>101</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1598792967</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1598792967</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>빛초롬네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>your2102@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1485-4124</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 계족산로5번안길 31 1층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/your2102</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>7</v>
+      </c>
+      <c r="R34" t="n">
+        <v>10</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>36170804</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36170804</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>동백꽃물들다</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>kimnow79@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1381-1828</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로94번길 11-27 하나로프라자 1층 110호</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_camellia_</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>43</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1606422036</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606422036</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>네일로빛</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>qhfkadb22@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1343-3796</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 대덕대로1486번길 93 1층 102호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.lovit_</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>120</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1136917432</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136917432</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>네일로그</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>nail_log@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 계족로690번길 21 선비마을1단지아파트</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2140736934</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2140736934</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>진희네일</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>woawoa22@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1321-6198</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌북로20번길 13-20 진희네일</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://zero.gongbiz.kr/shop/S000015885</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>50</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1966165168</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1966165168</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>손꾸락발꼬락</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>happy_snubh@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1385-3484</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 석봉북로9번길 31 1층 101호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>45</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1941716410</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1941716410</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>손끝패션</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bymom_@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1356-2541</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌북로 25 102호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>12</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1536112470</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1536112470</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>유잇뷰티</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>uit_hair@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진로796번길 111 1층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uit_beauty</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>60</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1027979492</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027979492</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>네일또봐요</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lyj3937@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1435-6745</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 덕암로181번길 20 1층, 네일,또봐요</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_FwxiQG</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>20</v>
+      </c>
+      <c r="R42" t="n">
+        <v>65</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1299352013</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1299352013</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>아이풋네일 문제성발톱 케어</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>im13star@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1423-1931</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 계족산로43번길 63 102호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/im13star</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>15</v>
+      </c>
+      <c r="R43" t="n">
+        <v>110</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1382165489</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1382165489</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>네일진</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kng026@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1379-3951</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 계족로521번길 91 1층 네일진</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailjin_l?igsh=MXN3anJ3b3lzNTZneA%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>15</v>
+      </c>
+      <c r="R44" t="n">
+        <v>144</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1230335417</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1230335417</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>네일루아</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>wldud0735@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1368-0289</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 중리북로 53 1층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>25</v>
+      </c>
+      <c r="R45" t="n">
+        <v>35</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1798664755</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798664755</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>오늘도네일</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>j2lang@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 중리로 68</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>19</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1183250733</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1183250733</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>소담네일&amp;뷰티</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>shinyg1022@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1306-7841</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 중리동로 18 1층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1256607977</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1256607977</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>온리비네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>hodu_chj_@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1473-4247</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진로796번길 19 1층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/only_b_nail?igsh=MTBseWQ3cnpnbjhuNg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>136</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1506180416</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1506180416</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>메이네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>dbsghrhkdvos@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1376-6610</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌북로19번길 17 1층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/m_a_y__nail</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1140135132</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1140135132</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>더숨뷰티</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>xiel_lover@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1310-3753</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 덕암로 186 3층 맨끝</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/xiel_lover</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>296</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>34</v>
+      </c>
+      <c r="R50" t="n">
+        <v>330</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1999867058</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1999867058</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>예뿜</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ospp5311@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1428-0631</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 중리남로8번길 127 1층 예뿜</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_yeppum_</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>22</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1842774698</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1842774698</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>쏭네일</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lgy0855@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1379-6630</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동서대로1809번길 23 1층 102호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ssonge_nail</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>109</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1827509366</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1827509366</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>진 네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>79hyojin@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1317-8042</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 비래동로15번길 2 B동 102호 진네일</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/79hyojin</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>17</v>
+      </c>
+      <c r="R53" t="n">
+        <v>74</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1429858526</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1429858526</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>루비에뷰티</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>eunhee_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1359-5249</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진북로32번길 14 1층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/eunhee_nail/224177918242</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>164</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>2028310053</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2028310053</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>리즈네일</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jozzin@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1397-3885</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로 178 보람코아상가 2층 221호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/leeznail</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>9</v>
+      </c>
+      <c r="R55" t="n">
+        <v>63</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1477184482</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1477184482</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>안나네일</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>dhqhfka274@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1381-4633</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 덕암로 233 1층 104호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>26</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>2054205754</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2054205754</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>제이의하루</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>rkdduswn0628@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1413-8521</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 석봉로43번길 16 101호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeijei_day</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>11</v>
+      </c>
+      <c r="R57" t="n">
+        <v>53</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1248159351</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1248159351</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>예쁘다뷰티</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>jinsk25@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1474-5802</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 비래서로26번길 13 1층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_alAxgG</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>27</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1712249969</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1712249969</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>라보떼</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>la_beaute7@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1310-5389</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로114번길 9 205호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1342260858</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1342260858</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>잇츠네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sspiria@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>042-639-6415</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로94번길 11-27 1층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sspiria</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>72</v>
+      </c>
+      <c r="R60" t="n">
+        <v>73</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>32315546</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32315546</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>네일드블랑 대전탄방점</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>hodu2425@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>대전광역시 서구 계룡로 599 2층 201-1호 네일드블랑</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_de_blanc_1/profilecard/?igsh=MWpibmtja2sydWc0NA==</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1598</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>284</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1882</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1455417829</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1455417829</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일 토마토</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>tomatonail2115@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1448-5110</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 대덕대로 1587 상가동 2층 207호 네일 토마토</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xipwxjn</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>30</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2090499164</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090499164</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>앨리스네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>lunefronde@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>042-626-3923</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로114번길 9</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>4</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1480642263</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1480642263</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>아름이음</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>dodamedu2023@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1364-3135</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 중리북로37번길 103 1층 101호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/areumium?igsh=ZXVwanNyOHNjZTBr&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>31</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2036078124</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036078124</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>네일보다</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>qmfosej@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1468-8832</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진동로24번길 5 1층 네일보다</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.boda?igsh=Mnd3ZHMyczRkOHg%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>7</v>
+      </c>
+      <c r="R65" t="n">
+        <v>61</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1959831123</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1959831123</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>하루앤네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>dydtjsdydtjs1225@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1343-4295</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 아리랑로 211 영진로얄상가동 1층 113호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/ZOZkmdyyJ</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>23</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2078592441</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2078592441</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>미손네일</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>classycp@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1368-1524</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 홍도로113번길 49 1층 101호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>4</v>
+      </c>
+      <c r="R67" t="n">
+        <v>14</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1472030101</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1472030101</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>여우손톱</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jayjayjensen@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1368-3773</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 중리북로37번길 66 1층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>2021897778</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2021897778</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>오신데렐라네일</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sol_revie@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1438-2161</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌로 16 101호 오~신데렐라네일</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>http://instagram.com/O_Shinderella_nail</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>6</v>
+      </c>
+      <c r="R69" t="n">
+        <v>24</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1212889971</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1212889971</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>타임네일 대전송촌점</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>yunamom0325@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1355-7775</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 송촌북로 29 타임네일</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/time_nai1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>71</v>
+      </c>
+      <c r="R70" t="n">
+        <v>284</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1005778111</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1005778111</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>네일도끌림</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>asahan214@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1379-0478</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로52번길 15 1층 101호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pckKn</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3</v>
+      </c>
+      <c r="R71" t="n">
+        <v>30</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1083802837</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1083802837</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>더예뻐네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>nail4season@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 동춘당로114번길 9</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>17</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1268260883</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1268260883</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>레푸스 중리점::다솜네일</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jahyunnail@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1338-4775</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 계족산로43번길 12 1층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jahyunnail</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>117</v>
+      </c>
+      <c r="R73" t="n">
+        <v>235</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>33500077</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33500077</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>쑥이네일</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dkclaghktkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진동로23번길 72 쑥이네일</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/ssuk2nail</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>60</v>
+      </c>
+      <c r="R74" t="n">
+        <v>247</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1822663199</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1822663199</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>오블리노</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>oblino_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 대덕대로1605번길 36 1층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xdfNZG</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>10</v>
+      </c>
+      <c r="R75" t="n">
+        <v>351</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1160454946</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1160454946</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>피부,체형관리</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>리온에스테틱</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>kjy302233@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1366-2548</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>대전광역시 대덕구 신탄진로218번길 62 현대아파트상가 가-4호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kjy302233</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>4</v>
+      </c>
+      <c r="R76" t="n">
+        <v>10</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1377311101</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1377311101</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/대덕구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/대덕구_네일샵.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일하이</t>
+          <t>아름이음</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dojulie@naver.com</t>
+          <t>dodamedu2023@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1424-7228</t>
+          <t>0507-1364-3135</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로4번길 7-6 1층</t>
+          <t>대전광역시 대덕구 중리북로37번길 103 1층 101호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhi_art</t>
+          <t>https://www.instagram.com/areumium?igsh=ZXVwanNyOHNjZTBr&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2065215101</t>
+          <t>2036078124</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065215101</t>
+          <t>https://m.place.naver.com/place/2036078124</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INDEEDMOOI</t>
+          <t>린네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>indeedmooi@naver.com</t>
+          <t>sini_97@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1346-6424</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 한밭대로1117번길 40 힙티크 1층 인디드무이</t>
+          <t>대전광역시 대덕구 대청로 61 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/indeed_mooi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>206</v>
+        <v>12</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1114773269</t>
+          <t>2002116511</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114773269</t>
+          <t>https://m.place.naver.com/place/2002116511</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뷰티사이언스네일몰</t>
+          <t>레푸스 중리점::다솜네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bcsacademy@naver.com</t>
+          <t>jahyunnail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1309-3380</t>
+          <t>0507-1338-4775</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 한남로 65 나동 3층 1호</t>
+          <t>대전광역시 대덕구 계족산로43번길 12 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jahyunnail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +780,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="R4" t="n">
-        <v>15</v>
+        <v>236</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1509821692</t>
+          <t>33500077</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509821692</t>
+          <t>https://m.place.naver.com/place/33500077</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>디앤네일</t>
+          <t>뷰티쑤</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>leo-tiger@naver.com</t>
+          <t>eternal_beauty_@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1336-7196</t>
+          <t>0507-1412-1152</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉로37번길 50 1층 건물</t>
+          <t>대전광역시 대덕구 비래동로32번길 12 뷰티쑤</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sfumCePe</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +874,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -894,22 +890,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>56</v>
+        <v>168</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1079560024</t>
+          <t>1837401843</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1079560024</t>
+          <t>https://m.place.naver.com/place/1837401843</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마벨네일</t>
+          <t>쏭네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yelee6080@naver.com</t>
+          <t>ssongnail01@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1338-1863</t>
+          <t>0507-1379-6630</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리남로8번길 7 1층</t>
+          <t>대전광역시 대덕구 동서대로1809번길 23 1층 102호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ssonge_nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,7 +968,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -993,17 +989,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1471715037</t>
+          <t>1827509366</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1471715037</t>
+          <t>https://m.place.naver.com/place/1827509366</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>미야,네일</t>
+          <t>리즈네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>asahan214@naver.com</t>
+          <t>jozzin@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1373-4162</t>
+          <t>0507-1397-3885</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 대덕대로 1555 상가동 1층 102호 미야네일</t>
+          <t>대전광역시 대덕구 동춘당로 178 보람코아상가 2층 221호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/miya_nail4162?igsh=MXgzaGhjbmNkOHVvNQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/leeznail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1892298393</t>
+          <t>1477184482</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892298393</t>
+          <t>https://m.place.naver.com/place/1477184482</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엉아네일</t>
+          <t>온리비네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c_younga@naver.com</t>
+          <t>hodu_chj_@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1360-5069</t>
+          <t>0507-1473-4247</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로 178 보람코아상가 141호</t>
+          <t>대전광역시 대덕구 신탄진로796번길 19 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/eongahnail</t>
+          <t>https://www.instagram.com/only_b_nail?igsh=MTBseWQ3cnpnbjhuNg%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>198</v>
+        <v>135</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1946869133</t>
+          <t>1506180416</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1946869133</t>
+          <t>https://m.place.naver.com/place/1506180416</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1218,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>빵실네일 &amp; 오로지푸스송촌점</t>
+          <t>더예뻐네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nailardi@naver.com</t>
+          <t>nail4season@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1235,12 +1231,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로48번길 25 1층</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.0__0</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>123</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>177863865</t>
+          <t>1268260883</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/177863865</t>
+          <t>https://m.place.naver.com/place/1268260883</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>지유네일</t>
+          <t>진 네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jiyunail@naver.com</t>
+          <t>79hyojin@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1431-2433</t>
+          <t>0507-1317-8042</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9 1층 151호</t>
+          <t>대전광역시 대덕구 비래동로15번길 2 B동 102호 진네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/79hyojin</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,12 +1340,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,17 +1361,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2007138642</t>
+          <t>1429858526</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007138642</t>
+          <t>https://m.place.naver.com/place/1429858526</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일유엘</t>
+          <t>안나네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uldesign17@naver.com</t>
+          <t>dhqhfka274@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1395-9046</t>
+          <t>0507-1381-4633</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉로37번길 12 1층 네일유엘</t>
+          <t>대전광역시 대덕구 덕암로 233 1층 104호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_yu.l</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,7 +1434,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1459,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1390260311</t>
+          <t>2054205754</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1390260311</t>
+          <t>https://m.place.naver.com/place/2054205754</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1496,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>린네일</t>
+          <t>쑥이네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sini_97@naver.com</t>
+          <t>dkclaghktkd@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1513,12 +1509,12 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 대청로 61 1층</t>
+          <t>대전광역시 대덕구 신탄진동로23번길 72 쑥이네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/ssuk2nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1549,17 +1545,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>186</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R12" t="n">
-        <v>11</v>
+        <v>246</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2002116511</t>
+          <t>1822663199</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002116511</t>
+          <t>https://m.place.naver.com/place/1822663199</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,25 +1586,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일해랑</t>
+          <t>미야,네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ayus_n@naver.com</t>
+          <t>asahan214@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1373-4162</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9</t>
+          <t>대전광역시 대덕구 대덕대로 1555 상가동 1층 102호 미야네일</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/miya_nail4162?igsh=MXgzaGhjbmNkOHVvNQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1639,17 +1639,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1199858879</t>
+          <t>1892298393</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1199858879</t>
+          <t>https://m.place.naver.com/place/1892298393</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1680,25 +1680,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엔에이뷰티</t>
+          <t>루비에뷰티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dang2709@naver.com</t>
+          <t>eunhee_nail@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1359-5249</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉로3번길 38 1층</t>
+          <t>대전광역시 대덕구 신탄진북로32번길 14 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty.nail_na</t>
+          <t>https://blog.naver.com/eunhee_nail/224177918242</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1713,7 +1717,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1724,7 +1728,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1733,13 +1737,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>393</v>
+        <v>160</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>400</v>
+        <v>165</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1748,17 +1752,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1313449424</t>
+          <t>2028310053</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1313449424</t>
+          <t>https://m.place.naver.com/place/2028310053</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1770,29 +1774,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>연네일</t>
+          <t>히토네일 대전탄방점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>wlsl9169@naver.com</t>
+          <t>rquoavewfs24536@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1385-7670</t>
+          <t>0507-1449-8960</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9 111호</t>
+          <t>대전광역시 서구 계룡로 639 2층 히토네일</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_JxbxmAn/chat</t>
+          <t>https://www.hitonail.com/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1807,7 +1811,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1827,13 +1831,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>56</v>
+        <v>2937</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="R15" t="n">
-        <v>58</v>
+        <v>3144</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1842,17 +1846,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1111773654</t>
+          <t>1221276034</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111773654</t>
+          <t>https://m.place.naver.com/place/1221276034</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1864,34 +1868,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>채우다 네일</t>
+          <t>네일도끌림</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nail_by_chaeuda@naver.com</t>
+          <t>asahan214@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1322-8628</t>
+          <t>0507-1379-0478</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 비래서로10번길 76 1층.채우다네일</t>
+          <t>대전광역시 대덕구 동춘당로52번길 15 1층 101호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sO65IRDd</t>
+          <t>http://pf.kakao.com/_pckKn</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1921,13 +1925,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="Q16" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1940,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38427932</t>
+          <t>1083802837</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38427932</t>
+          <t>https://m.place.naver.com/place/1083802837</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2056,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>끌밋네일</t>
+          <t>네일유엘</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pmh2317@naver.com</t>
+          <t>uldesign17@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1310-0340</t>
+          <t>0507-1395-9046</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진북로 41 1층</t>
+          <t>대전광역시 대덕구 석봉로37번길 12 1층 네일유엘</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sjlRfxXg</t>
+          <t>https://www.instagram.com/nail_yu.l</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2100,7 +2104,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2109,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2007045292</t>
+          <t>1390260311</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007045292</t>
+          <t>https://m.place.naver.com/place/1390260311</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2146,39 +2150,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>손톱깎이</t>
+          <t>네일하이</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nagi96@naver.com</t>
+          <t>dojulie@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>042-633-6619</t>
+          <t>0507-1424-7228</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로19번길 8-21</t>
+          <t>대전광역시 대덕구 송촌북로4번길 7-6 1층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://0426336619.tshome.co.kr/menu.php</t>
+          <t>https://www.instagram.com/nailhi_art</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2203,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1439652285</t>
+          <t>2065215101</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1439652285</t>
+          <t>https://m.place.naver.com/place/2065215101</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2240,34 +2244,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일리온드</t>
+          <t>차밍네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mum9177@naver.com</t>
+          <t>bdhyuniee@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1464-1483</t>
+          <t>0507-1346-0584</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 대청로 43 상가 B동 211호</t>
+          <t>대전광역시 대덕구 한남로 33 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_PUazG</t>
+          <t>https://www.instagram.com/charmingnail__</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2288,7 +2292,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2297,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1568879186</t>
+          <t>2030664237</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568879186</t>
+          <t>https://m.place.naver.com/place/2030664237</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2334,25 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>네일쿱스</t>
+          <t>푸스케어 대전신탄진점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>zmzpop@naver.com</t>
+          <t>fusscaer_sintanjin@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1440-9218</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진로218번길 25</t>
+          <t>대전광역시 대덕구 석봉로37번길 30 2층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fusscaer_sintanjin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2362,12 +2370,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2387,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="Q21" t="n">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2402,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1101217149</t>
+          <t>1217159353</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101217149</t>
+          <t>https://m.place.naver.com/place/1217159353</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2424,34 +2432,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>유니즈네일</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>gksmfz7@naver.com</t>
-        </is>
-      </c>
+          <t>네일 토마토</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1328-9654</t>
+          <t>0507-1448-5110</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 한밭대로1130번길 10 1층 유니즈 네일</t>
+          <t>대전광역시 대덕구 대덕대로 1587 상가동 2층 207호 네일 토마토</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/u_needs_nail</t>
+          <t>http://pf.kakao.com/_xipwxjn</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2472,7 +2476,7 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2481,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2496,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1542052913</t>
+          <t>2090499164</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1542052913</t>
+          <t>https://m.place.naver.com/place/2090499164</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2518,29 +2522,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일뭐해</t>
+          <t>끌밋네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mementomori-24@naver.com</t>
+          <t>pmh2317@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1362-8739</t>
+          <t>0507-1310-0340</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9 1층 125호</t>
+          <t>대전광역시 대덕구 신탄진북로 41 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sjlRfxXg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2550,7 +2554,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2566,22 +2570,22 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2590,17 +2594,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2047980305</t>
+          <t>2007045292</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047980305</t>
+          <t>https://m.place.naver.com/place/2007045292</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2612,29 +2616,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>네일&amp;패디쿱스</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>som_a621@naver.com</t>
-        </is>
-      </c>
+          <t>오신데렐라네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1474-2311</t>
+          <t>0507-1438-2161</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진로218번길 25 1층 102호</t>
+          <t>대전광역시 대덕구 송촌로 16 101호 오~신데렐라네일</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/O_Shinderella_nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2665,17 +2665,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q24" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2684,17 +2684,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1009458693</t>
+          <t>1212889971</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1009458693</t>
+          <t>https://m.place.naver.com/place/1212889971</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2706,29 +2706,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>러브희</t>
+          <t>제이의하루</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>lbang9@naver.com</t>
+          <t>rkdduswn0628@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1449-1391</t>
+          <t>0507-1413-8521</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 비래동로39번길 9 1층 LUVHEE</t>
+          <t>대전광역시 대덕구 석봉로43번길 16 101호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luvhee.nails</t>
+          <t>https://www.instagram.com/jeijei_day</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>471</v>
+        <v>42</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>472</v>
+        <v>53</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2778,17 +2778,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1191517495</t>
+          <t>1248159351</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1191517495</t>
+          <t>https://m.place.naver.com/place/1248159351</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2800,34 +2800,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>푸스케어 대전신탄진점</t>
+          <t>예쁘다뷰티</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fusscaer_sintanjin@naver.com</t>
+          <t>jinsk25@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1440-9218</t>
+          <t>0507-1474-5802</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉로37번길 30 2층</t>
+          <t>대전광역시 대덕구 비래서로26번길 13 1층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fusscaer_sintanjin</t>
+          <t>http://pf.kakao.com/_alAxgG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2848,22 +2848,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>145</v>
+        <v>27</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2872,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1217159353</t>
+          <t>1712249969</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1217159353</t>
+          <t>https://m.place.naver.com/place/1712249969</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2894,30 +2894,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>리미네일</t>
+          <t>타임네일 대전송촌점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>isky6407@naver.com</t>
+          <t>yunamom0325@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1355-7775</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로48번길 22 1층 리미네일</t>
+          <t>대전광역시 대덕구 송촌북로 29 타임네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yvVCxj</t>
+          <t>http://www.instagram.com/time_nai1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2938,7 +2942,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2947,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="R27" t="n">
-        <v>130</v>
+        <v>284</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1524115972</t>
+          <t>1005778111</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1524115972</t>
+          <t>https://m.place.naver.com/place/1005778111</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2984,24 +2988,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아이러브네일</t>
+          <t>마벨네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>saddysad@naver.com</t>
+          <t>yelee6080@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>042-286-8006</t>
+          <t>0507-1338-1863</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진로 839</t>
+          <t>대전광역시 대덕구 중리남로8번길 7 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3041,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3060,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1545070428</t>
+          <t>1471715037</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1545070428</t>
+          <t>https://m.place.naver.com/place/1471715037</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3078,20 +3082,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>더예쁜네일</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>sjynobby@naver.com</t>
-        </is>
-      </c>
+          <t>네일&amp;패디쿱스</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1474-2311</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로 6 1층</t>
+          <t>대전광역시 대덕구 신탄진로218번길 25 1층 102호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3131,13 +3135,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,17 +3150,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1236643304</t>
+          <t>1009458693</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236643304</t>
+          <t>https://m.place.naver.com/place/1009458693</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3168,29 +3172,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뷰티쑤</t>
+          <t>라보떼</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>eternal_beauty_@naver.com</t>
+          <t>la_beaute7@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1412-1152</t>
+          <t>0507-1310-5389</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 비래동로32번길 12 뷰티쑤</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9 205호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sfumCePe</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3200,7 +3204,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3216,22 +3220,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3240,17 +3244,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1837401843</t>
+          <t>1342260858</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1837401843</t>
+          <t>https://m.place.naver.com/place/1342260858</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3262,34 +3266,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>차밍네일</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>hyunah0701@naver.com</t>
-        </is>
-      </c>
+          <t>리미네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0507-1346-0584</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 한남로 33 1층</t>
+          <t>대전광역시 대덕구 동춘당로48번길 22 1층 리미네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/charmingnail__</t>
+          <t>http://pf.kakao.com/_yvVCxj</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3310,7 +3306,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3319,13 +3315,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3334,17 +3330,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2030664237</t>
+          <t>1524115972</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2030664237</t>
+          <t>https://m.place.naver.com/place/1524115972</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3356,29 +3352,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>쮸샵</t>
+          <t>빛초롬네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>herrimi@naver.com</t>
+          <t>your2102@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>042-345-8384</t>
+          <t>0507-1485-4124</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉로38번길 13 하늘빛교회</t>
+          <t>대전광역시 대덕구 계족산로5번안길 31 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/your2102</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3388,12 +3384,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3416,10 +3412,10 @@
         <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R32" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3428,17 +3424,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1125107179</t>
+          <t>36170804</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1125107179</t>
+          <t>https://m.place.naver.com/place/36170804</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3450,34 +3446,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일 쁘 셀</t>
+          <t>INDEEDMOOI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>orr0427@naver.com</t>
+          <t>indeedmooi@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1382-2219</t>
+          <t>0507-1346-6424</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 한남로17번길 38</t>
+          <t>대전광역시 대덕구 한밭대로1117번길 40 힙티크 1층 인디드무이</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xowGLxj</t>
+          <t>https://www.instagram.com/indeed_mooi</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3498,7 +3494,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3507,13 +3503,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>101</v>
+        <v>208</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3522,17 +3518,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1598792967</t>
+          <t>1114773269</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598792967</t>
+          <t>https://m.place.naver.com/place/1114773269</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3544,29 +3540,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>빛초롬네일</t>
+          <t>예뿜</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>your2102@naver.com</t>
+          <t>ospp5311@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1485-4124</t>
+          <t>0507-1428-0631</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 계족산로5번안길 31 1층</t>
+          <t>대전광역시 대덕구 중리남로8번길 127 1층 예뿜</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/your2102</t>
+          <t>https://www.instagram.com/_yeppum_</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3581,7 +3577,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3597,17 +3593,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3616,17 +3612,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>36170804</t>
+          <t>1842774698</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36170804</t>
+          <t>https://m.place.naver.com/place/1842774698</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3638,29 +3634,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>동백꽃물들다</t>
+          <t>여우손톱</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kimnow79@naver.com</t>
+          <t>jayjayjensen@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1381-1828</t>
+          <t>0507-1368-3773</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로94번길 11-27 하나로프라자 1층 110호</t>
+          <t>대전광역시 대덕구 중리북로37번길 66 1층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_camellia_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3670,7 +3666,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3691,17 +3687,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3706,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1606422036</t>
+          <t>2021897778</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1606422036</t>
+          <t>https://m.place.naver.com/place/2021897778</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3732,34 +3728,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일로빛</t>
+          <t>진희네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>qhfkadb22@naver.com</t>
+          <t>woawoa22@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1343-3796</t>
+          <t>0507-1321-6198</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 대덕대로1486번길 93 1층 102호</t>
+          <t>대전광역시 대덕구 송촌북로20번길 13-20 진희네일</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.lovit_</t>
+          <t>https://zero.gongbiz.kr/shop/S000015885</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3780,7 +3776,7 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3789,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3800,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1136917432</t>
+          <t>1966165168</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136917432</t>
+          <t>https://m.place.naver.com/place/1966165168</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3826,20 +3822,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>네일로그</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>nail_log@naver.com</t>
-        </is>
-      </c>
+          <t>미손네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1368-1524</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 계족로690번길 21 선비마을1단지아파트</t>
+          <t>대전광역시 대덕구 홍도로113번길 49 1층 101호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3879,13 +3875,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3894,17 +3890,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2140736934</t>
+          <t>1472030101</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2140736934</t>
+          <t>https://m.place.naver.com/place/1472030101</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3916,29 +3912,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>진희네일</t>
+          <t>연네일</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>woawoa22@naver.com</t>
+          <t>wlsl9169@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1321-6198</t>
+          <t>0507-1385-7670</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로20번길 13-20 진희네일</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9 111호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://zero.gongbiz.kr/shop/S000015885</t>
+          <t>http://pf.kakao.com/_JxbxmAn/chat</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3973,13 +3969,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3988,17 +3984,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1966165168</t>
+          <t>1111773654</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1966165168</t>
+          <t>https://m.place.naver.com/place/1111773654</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4010,24 +4006,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>손꾸락발꼬락</t>
+          <t>오늘도네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>happy_snubh@naver.com</t>
+          <t>j2lang@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0507-1385-3484</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉북로9번길 31 1층 101호</t>
+          <t>대전광역시 대덕구 중리로 68</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4067,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4082,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1941716410</t>
+          <t>1183250733</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1941716410</t>
+          <t>https://m.place.naver.com/place/1183250733</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4104,39 +4096,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>손끝패션</t>
+          <t>오블리노</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bymom_@naver.com</t>
+          <t>oblino_nail@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0507-1356-2541</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로 25 102호</t>
+          <t>대전광역시 대덕구 대덕대로1605번길 36 1층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xdfNZG</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4152,22 +4140,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>12</v>
+        <v>345</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R40" t="n">
-        <v>12</v>
+        <v>355</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4176,17 +4164,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1536112470</t>
+          <t>1160454946</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1536112470</t>
+          <t>https://m.place.naver.com/place/1160454946</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4198,25 +4186,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>유잇뷰티</t>
+          <t>뷰티사이언스네일몰</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>uit_hair@naver.com</t>
+          <t>bcsacademy@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1309-3380</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진로796번길 111 1층</t>
+          <t>대전광역시 대덕구 한남로 65 나동 3층 1호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uit_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4226,7 +4218,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4247,17 +4239,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R41" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4266,17 +4258,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1027979492</t>
+          <t>1509821692</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027979492</t>
+          <t>https://m.place.naver.com/place/1509821692</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4288,29 +4280,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일또봐요</t>
+          <t>네일리온드</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>lyj3937@naver.com</t>
+          <t>yj5229948@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1435-6745</t>
+          <t>0507-1464-1483</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 덕암로181번길 20 1층, 네일,또봐요</t>
+          <t>대전광역시 대덕구 대청로 43 상가 B동 211호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_FwxiQG</t>
+          <t>http://pf.kakao.com/_PUazG</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4345,13 +4337,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4360,17 +4352,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1299352013</t>
+          <t>1568879186</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299352013</t>
+          <t>https://m.place.naver.com/place/1568879186</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4382,29 +4374,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아이풋네일 문제성발톱 케어</t>
+          <t>더예쁜네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>im13star@naver.com</t>
+          <t>sjynobby@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1423-1931</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 계족산로43번길 63 102호</t>
+          <t>대전광역시 대덕구 송촌북로 6 1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/im13star</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4414,12 +4402,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4435,18 +4423,18 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
         <v>15</v>
       </c>
-      <c r="R43" t="n">
-        <v>110</v>
-      </c>
       <c r="S43" t="inlineStr">
         <is>
           <t>X</t>
@@ -4454,17 +4442,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1382165489</t>
+          <t>1236643304</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1382165489</t>
+          <t>https://m.place.naver.com/place/1236643304</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4476,29 +4464,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>네일진</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>kng026@naver.com</t>
-        </is>
-      </c>
+          <t>지유네일</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1379-3951</t>
+          <t>0507-1431-2433</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 계족로521번길 91 1층 네일진</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9 1층 151호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailjin_l?igsh=MXN3anJ3b3lzNTZneA%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4508,7 +4492,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4529,17 +4513,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4548,17 +4532,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1230335417</t>
+          <t>2007138642</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230335417</t>
+          <t>https://m.place.naver.com/place/2007138642</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4570,39 +4554,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>네일루아</t>
+          <t>네일또봐요</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wldud0735@naver.com</t>
+          <t>lyj3937@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1368-0289</t>
+          <t>0507-1435-6745</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리북로 53 1층</t>
+          <t>대전광역시 대덕구 덕암로181번길 20 1층, 네일,또봐요</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_FwxiQG</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4618,22 +4602,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="Q45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R45" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4642,17 +4626,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1798664755</t>
+          <t>1299352013</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798664755</t>
+          <t>https://m.place.naver.com/place/1299352013</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4664,25 +4648,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>오늘도네일</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>j2lang@naver.com</t>
-        </is>
-      </c>
+          <t>빵실네일 &amp; 오로지푸스송촌점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리로 68</t>
+          <t>대전광역시 대덕구 동춘당로48번길 25 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.0__0</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4692,7 +4672,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4713,17 +4693,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>19</v>
+        <v>123</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="R46" t="n">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4732,17 +4712,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1183250733</t>
+          <t>177863865</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1183250733</t>
+          <t>https://m.place.naver.com/place/177863865</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4754,24 +4734,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>소담네일&amp;뷰티</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>shinyg1022@naver.com</t>
-        </is>
-      </c>
+          <t>앨리스네일</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1306-7841</t>
+          <t>042-626-3923</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리동로 18 1층</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4826,17 +4802,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1256607977</t>
+          <t>1480642263</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256607977</t>
+          <t>https://m.place.naver.com/place/1480642263</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4848,29 +4824,25 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>온리비네일</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>hodu_chj_@naver.com</t>
-        </is>
-      </c>
+          <t>러브희</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1473-4247</t>
+          <t>0507-1449-1391</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진로796번길 19 1층</t>
+          <t>대전광역시 대덕구 비래동로39번길 9 1층 LUVHEE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/only_b_nail?igsh=MTBseWQ3cnpnbjhuNg%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/luvhee.nails</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4905,13 +4877,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>134</v>
+        <v>474</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>136</v>
+        <v>475</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,17 +4892,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1506180416</t>
+          <t>1191517495</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506180416</t>
+          <t>https://m.place.naver.com/place/1191517495</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4942,29 +4914,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>메이네일</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>dbsghrhkdvos@naver.com</t>
-        </is>
-      </c>
+          <t>네일보다</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1376-6610</t>
+          <t>0507-1468-8832</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로19번길 17 1층</t>
+          <t>대전광역시 대덕구 신탄진동로24번길 5 1층 네일보다</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/m_a_y__nail</t>
+          <t>https://www.instagram.com/nail.boda?igsh=Mnd3ZHMyczRkOHg%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4999,13 +4967,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,17 +4982,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1140135132</t>
+          <t>1959831123</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1140135132</t>
+          <t>https://m.place.naver.com/place/1959831123</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5036,29 +5004,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>더숨뷰티</t>
+          <t>유니즈네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>xiel_lover@naver.com</t>
+          <t>gksmfz7@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1310-3753</t>
+          <t>0507-1328-9654</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 덕암로 186 3층 맨끝</t>
+          <t>대전광역시 대덕구 한밭대로1130번길 10 1층 유니즈 네일</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/xiel_lover</t>
+          <t>https://www.instagram.com/u_needs_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5073,7 +5041,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5089,17 +5057,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>296</v>
+        <v>26</v>
       </c>
       <c r="Q50" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="R50" t="n">
-        <v>330</v>
+        <v>35</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,17 +5076,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1999867058</t>
+          <t>1542052913</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1999867058</t>
+          <t>https://m.place.naver.com/place/1542052913</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5130,29 +5098,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>예뿜</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ospp5311@naver.com</t>
-        </is>
-      </c>
+          <t>채우다 네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1428-0631</t>
+          <t>0507-1322-8628</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리남로8번길 127 1층 예뿜</t>
+          <t>대전광역시 대덕구 비래서로10번길 76 1층.채우다네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_yeppum_</t>
+          <t>https://open.kakao.com/o/sO65IRDd</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5178,7 +5142,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5187,13 +5151,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R51" t="n">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5166,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1842774698</t>
+          <t>38427932</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842774698</t>
+          <t>https://m.place.naver.com/place/38427932</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5224,29 +5188,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>쏭네일</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>lgy0855@naver.com</t>
-        </is>
-      </c>
+          <t>네일로빛</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1379-6630</t>
+          <t>0507-1343-3796</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동서대로1809번길 23 1층 102호</t>
+          <t>대전광역시 대덕구 대덕대로1486번길 93 1층 102호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssonge_nail</t>
+          <t>https://www.instagram.com/nail.lovit_</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5281,13 +5241,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R52" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,17 +5256,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1827509366</t>
+          <t>1136917432</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827509366</t>
+          <t>https://m.place.naver.com/place/1136917432</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5318,29 +5278,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>진 네일</t>
+          <t>네일뭐해</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>79hyojin@naver.com</t>
+          <t>sarangst7@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1317-8042</t>
+          <t>0507-1362-8739</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 비래동로15번길 2 B동 102호 진네일</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9 1층 125호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/79hyojin</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5350,12 +5310,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5371,17 +5331,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,17 +5350,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1429858526</t>
+          <t>2047980305</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429858526</t>
+          <t>https://m.place.naver.com/place/2047980305</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5412,29 +5372,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>루비에뷰티</t>
+          <t>메이네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>eunhee_nail@naver.com</t>
+          <t>dbsghrhkdvos@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1359-5249</t>
+          <t>0507-1376-6610</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진북로32번길 14 1층</t>
+          <t>대전광역시 대덕구 송촌북로19번길 17 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/eunhee_nail/224177918242</t>
+          <t>https://www.instagram.com/m_a_y__nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5449,7 +5409,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5469,13 +5429,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5444,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2028310053</t>
+          <t>1140135132</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2028310053</t>
+          <t>https://m.place.naver.com/place/1140135132</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5506,29 +5466,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>리즈네일</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>jozzin@naver.com</t>
-        </is>
-      </c>
+          <t>네일루아</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1397-3885</t>
+          <t>0507-1368-0289</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로 178 보람코아상가 2층 221호</t>
+          <t>대전광역시 대덕구 중리북로 53 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leeznail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5538,7 +5494,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5559,17 +5515,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="R55" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5578,17 +5534,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1477184482</t>
+          <t>1798664755</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477184482</t>
+          <t>https://m.place.naver.com/place/1798664755</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5600,34 +5556,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>안나네일</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>dhqhfka274@naver.com</t>
-        </is>
-      </c>
+          <t>손톱깎이</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1381-4633</t>
+          <t>042-633-6619</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 덕암로 233 1층 104호</t>
+          <t>대전광역시 대덕구 송촌북로19번길 8-21</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://0426336619.tshome.co.kr/menu.php</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -5653,17 +5605,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="R56" t="n">
-        <v>26</v>
+        <v>150</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,17 +5624,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2054205754</t>
+          <t>1439652285</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054205754</t>
+          <t>https://m.place.naver.com/place/1439652285</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5694,29 +5646,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>제이의하루</t>
+          <t>더숨뷰티</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>rkdduswn0628@naver.com</t>
+          <t>xiel_lover@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1413-8521</t>
+          <t>0507-1310-3753</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 석봉로43번길 16 101호</t>
+          <t>대전광역시 대덕구 덕암로 186 3층 맨끝</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jeijei_day</t>
+          <t>https://blog.naver.com/xiel_lover</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5731,7 +5683,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5747,17 +5699,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>42</v>
+        <v>297</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="R57" t="n">
-        <v>53</v>
+        <v>331</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5718,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1248159351</t>
+          <t>1999867058</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1248159351</t>
+          <t>https://m.place.naver.com/place/1999867058</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5788,39 +5740,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>예쁘다뷰티</t>
+          <t>아이러브네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jinsk25@naver.com</t>
+          <t>saddysad@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1474-5802</t>
+          <t>042-286-8006</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 비래서로26번길 13 1층</t>
+          <t>대전광역시 대덕구 신탄진로 839</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_alAxgG</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5836,22 +5788,22 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5812,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1712249969</t>
+          <t>1545070428</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1712249969</t>
+          <t>https://m.place.naver.com/place/1545070428</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5882,24 +5834,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>라보떼</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>la_beaute7@naver.com</t>
-        </is>
-      </c>
+          <t>네일해랑</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1310-5389</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9 205호</t>
+          <t>대전광역시 대덕구 동춘당로114번길 9</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5939,13 +5883,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +5898,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1342260858</t>
+          <t>1199858879</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342260858</t>
+          <t>https://m.place.naver.com/place/1199858879</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5976,34 +5920,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>잇츠네일</t>
+          <t>네일 쁘 셀</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sspiria@naver.com</t>
+          <t>0in4323@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>042-639-6415</t>
+          <t>0507-1382-2219</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로94번길 11-27 1층</t>
+          <t>대전광역시 대덕구 한남로17번길 38</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sspiria</t>
+          <t>https://pf.kakao.com/_xowGLxj</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6013,7 +5957,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6024,22 +5968,22 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P60" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>72</v>
-      </c>
       <c r="R60" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,17 +5992,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>32315546</t>
+          <t>1598792967</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32315546</t>
+          <t>https://m.place.naver.com/place/1598792967</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6070,25 +6014,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일드블랑 대전탄방점</t>
+          <t>네일진</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hodu2425@naver.com</t>
+          <t>kng026@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1379-3951</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대전광역시 서구 계룡로 599 2층 201-1호 네일드블랑</t>
+          <t>대전광역시 대덕구 계족로521번길 91 1층 네일진</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_blanc_1/profilecard/?igsh=MWpibmtja2sydWc0NA==</t>
+          <t>https://www.instagram.com/nailjin_l?igsh=MXN3anJ3b3lzNTZneA%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,13 +6071,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1598</v>
+        <v>129</v>
       </c>
       <c r="Q61" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="R61" t="n">
-        <v>1882</v>
+        <v>144</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6086,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1455417829</t>
+          <t>1230335417</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1455417829</t>
+          <t>https://m.place.naver.com/place/1230335417</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6160,34 +6108,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일 토마토</t>
+          <t>엔에이뷰티</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tomatonail2115@naver.com</t>
+          <t>dang2709@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0507-1448-5110</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 대덕대로 1587 상가동 2층 207호 네일 토마토</t>
+          <t>대전광역시 대덕구 석봉로3번길 38 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xipwxjn</t>
+          <t>https://www.instagram.com/beauty.nail_na</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6217,13 +6161,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>30</v>
+        <v>393</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R62" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6176,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>2090499164</t>
+          <t>1313449424</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090499164</t>
+          <t>https://m.place.naver.com/place/1313449424</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6254,24 +6198,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>앨리스네일</t>
+          <t>손꾸락발꼬락</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>lunefronde@naver.com</t>
+          <t>polkadot127@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>042-626-3923</t>
+          <t>0507-1385-3484</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9</t>
+          <t>대전광역시 대덕구 석봉북로9번길 31 1층 101호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6311,13 +6255,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6270,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1480642263</t>
+          <t>1941716410</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1480642263</t>
+          <t>https://m.place.naver.com/place/1941716410</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6348,29 +6292,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>아름이음</t>
+          <t>잇츠네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dodamedu2023@naver.com</t>
+          <t>sspiria@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1364-3135</t>
+          <t>042-639-6415</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리북로37번길 103 1층 101호</t>
+          <t>대전광역시 대덕구 동춘당로94번길 11-27 1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/areumium?igsh=ZXVwanNyOHNjZTBr&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/sspiria</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6385,7 +6329,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6401,17 +6345,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="R64" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,17 +6364,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>2036078124</t>
+          <t>32315546</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036078124</t>
+          <t>https://m.place.naver.com/place/32315546</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6442,29 +6386,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일보다</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>qmfosej@naver.com</t>
-        </is>
-      </c>
+          <t>쮸샵</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1468-8832</t>
+          <t>042-345-8384</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진동로24번길 5 1층 네일보다</t>
+          <t>대전광역시 대덕구 석봉로38번길 13 하늘빛교회</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.boda?igsh=Mnd3ZHMyczRkOHg%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6474,7 +6414,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6495,17 +6435,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,17 +6454,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1959831123</t>
+          <t>1125107179</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1959831123</t>
+          <t>https://m.place.naver.com/place/1125107179</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6536,44 +6476,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>하루앤네일</t>
+          <t>아이풋네일 문제성발톱 케어</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>dydtjsdydtjs1225@naver.com</t>
+          <t>im13star@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1343-4295</t>
+          <t>0507-1423-1931</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 아리랑로 211 영진로얄상가동 1층 113호</t>
+          <t>대전광역시 대덕구 계족산로43번길 63 102호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/ZOZkmdyyJ</t>
+          <t>https://blog.naver.com/im13star</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6584,7 +6524,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6593,13 +6533,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="Q66" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R66" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,17 +6548,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2078592441</t>
+          <t>1382165489</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2078592441</t>
+          <t>https://m.place.naver.com/place/1382165489</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6630,29 +6570,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>미손네일</t>
+          <t>엉아네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>classycp@naver.com</t>
+          <t>hyun_0918_@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1368-1524</t>
+          <t>0507-1360-5069</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 홍도로113번길 49 1층 101호</t>
+          <t>대전광역시 대덕구 동춘당로 178 보람코아상가 141호</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/eongahnail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6662,7 +6602,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -6683,17 +6623,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>198</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>14</v>
+        <v>201</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,17 +6642,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1472030101</t>
+          <t>1946869133</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472030101</t>
+          <t>https://m.place.naver.com/place/1946869133</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6724,24 +6664,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>여우손톱</t>
+          <t>디앤네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jayjayjensen@naver.com</t>
+          <t>leo-tiger@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1368-3773</t>
+          <t>0507-1336-7196</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 중리북로37번길 66 1층</t>
+          <t>대전광역시 대덕구 석봉로37번길 50 1층 건물</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6781,13 +6721,13 @@
         </is>
       </c>
       <c r="P68" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>2</v>
-      </c>
       <c r="R68" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6796,17 +6736,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2021897778</t>
+          <t>1079560024</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2021897778</t>
+          <t>https://m.place.naver.com/place/1079560024</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6818,29 +6758,21 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>오신데렐라네일</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>sol_revie@naver.com</t>
-        </is>
-      </c>
+          <t>네일로그</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>0507-1438-2161</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌로 16 101호 오~신데렐라네일</t>
+          <t>대전광역시 대덕구 계족로690번길 21 선비마을1단지아파트</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/O_Shinderella_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6850,7 +6782,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6871,17 +6803,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6890,17 +6822,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1212889971</t>
+          <t>2140736934</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1212889971</t>
+          <t>https://m.place.naver.com/place/2140736934</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6912,29 +6844,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>타임네일 대전송촌점</t>
+          <t>네일쿱스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yunamom0325@naver.com</t>
+          <t>zmzpop@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1355-7775</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 송촌북로 29 타임네일</t>
+          <t>대전광역시 대덕구 신탄진로218번길 25</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/time_nai1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6944,7 +6872,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6965,17 +6893,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="R70" t="n">
-        <v>284</v>
+        <v>6</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6984,17 +6912,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1005778111</t>
+          <t>1101217149</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005778111</t>
+          <t>https://m.place.naver.com/place/1101217149</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7006,34 +6934,30 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일도끌림</t>
+          <t>유잇뷰티</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>asahan214@naver.com</t>
+          <t>sarah_1217@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1379-0478</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로52번길 15 1층 101호</t>
+          <t>대전광역시 대덕구 신탄진로796번길 111 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pckKn</t>
+          <t>https://www.instagram.com/uit_beauty</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7054,7 +6978,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7063,13 +6987,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7078,17 +7002,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1083802837</t>
+          <t>1027979492</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083802837</t>
+          <t>https://m.place.naver.com/place/1027979492</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7100,30 +7024,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>더예뻐네일</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>nail4season@naver.com</t>
-        </is>
-      </c>
+          <t>하루앤네일</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1343-4295</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 동춘당로114번길 9</t>
+          <t>대전광역시 대덕구 아리랑로 211 영진로얄상가동 1층 113호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://toss.place/_lb/ZOZkmdyyJ</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7144,22 +7068,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,17 +7092,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1268260883</t>
+          <t>2078592441</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1268260883</t>
+          <t>https://m.place.naver.com/place/2078592441</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7190,29 +7114,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>레푸스 중리점::다솜네일</t>
+          <t>손끝패션</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>jahyunnail@naver.com</t>
+          <t>bymom_@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1338-4775</t>
+          <t>0507-1356-2541</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 계족산로43번길 12 1층</t>
+          <t>대전광역시 대덕구 송촌북로 25 102호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jahyunnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7222,12 +7146,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7243,17 +7167,17 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>118</v>
+        <v>12</v>
       </c>
       <c r="Q73" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>235</v>
+        <v>12</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7262,17 +7186,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>33500077</t>
+          <t>1536112470</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33500077</t>
+          <t>https://m.place.naver.com/place/1536112470</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7284,25 +7208,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>쑥이네일</t>
+          <t>소담네일&amp;뷰티</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>dkclaghktkd@naver.com</t>
+          <t>shinyg1022@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1306-7841</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 신탄진동로23번길 72 쑥이네일</t>
+          <t>대전광역시 대덕구 중리동로 18 1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ssuk2nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7312,7 +7240,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7333,17 +7261,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="Q74" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>247</v>
+        <v>4</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7352,17 +7280,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1822663199</t>
+          <t>1256607977</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1822663199</t>
+          <t>https://m.place.naver.com/place/1256607977</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7374,30 +7302,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>오블리노</t>
+          <t>동백꽃물들다</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>oblino_nail@naver.com</t>
+          <t>kimnow79@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1381-1828</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대전광역시 대덕구 대덕대로1605번길 36 1층</t>
+          <t>대전광역시 대덕구 동춘당로94번길 11-27 하나로프라자 1층 110호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdfNZG</t>
+          <t>https://www.instagram.com/nail_camellia_</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7418,7 +7350,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7427,13 +7359,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>341</v>
+        <v>41</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>351</v>
+        <v>43</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,17 +7374,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1160454946</t>
+          <t>1606422036</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160454946</t>
+          <t>https://m.place.naver.com/place/1606422036</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7478,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
